--- a/演示/真实数据拆配排表吧唧.xlsx
+++ b/演示/真实数据拆配排表吧唧.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RenSheet\演示\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E70741E-F556-4DF7-BDDE-5D41A02F067F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0D34C4-CDD8-4587-9C54-76BACF039D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,36 +471,6 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
-        <v>45</v>
-      </c>
-      <c r="C3">
-        <v>45</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>29</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>64</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>15</v>
-      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
